--- a/data/trans_orig/P36B12-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B12-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25976</t>
+          <t>26196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50201</t>
+          <t>49549</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33741</t>
+          <t>32909</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61672</t>
+          <t>58731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63769</t>
+          <t>65887</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100394</t>
+          <t>101141</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>192869</t>
+          <t>193191</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>242406</t>
+          <t>244152</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>256494</t>
+          <t>255293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>314413</t>
+          <t>312384</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>460323</t>
+          <t>463436</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>540093</t>
+          <t>540038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>491038</t>
+          <t>494332</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>557930</t>
+          <t>554857</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>700977</t>
+          <t>700758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>774953</t>
+          <t>770419</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1212150</t>
+          <t>1217004</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1305065</t>
+          <t>1312374</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>192063</t>
+          <t>194275</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>245544</t>
+          <t>246890</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>201909</t>
+          <t>206368</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>260163</t>
+          <t>256852</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>411936</t>
+          <t>414089</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>487449</t>
+          <t>486108</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21757</t>
+          <t>21812</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45720</t>
+          <t>45094</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12443</t>
+          <t>12627</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30836</t>
+          <t>30899</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37960</t>
+          <t>38459</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>67362</t>
+          <t>67843</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22534</t>
+          <t>22260</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45528</t>
+          <t>45686</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30157</t>
+          <t>30643</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57066</t>
+          <t>57079</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59517</t>
+          <t>58766</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95910</t>
+          <t>94001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305552</t>
+          <t>307587</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>372630</t>
+          <t>371043</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>237432</t>
+          <t>235305</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>296119</t>
+          <t>301395</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>558334</t>
+          <t>562347</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>645051</t>
+          <t>648349</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>903238</t>
+          <t>902706</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>983573</t>
+          <t>987159</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>935039</t>
+          <t>930153</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1010967</t>
+          <t>1010148</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1852523</t>
+          <t>1861938</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1971395</t>
+          <t>1973765</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,3%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>306561</t>
+          <t>303412</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>375746</t>
+          <t>374190</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>248779</t>
+          <t>250620</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>312044</t>
+          <t>312968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>573304</t>
+          <t>572476</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>665038</t>
+          <t>661649</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25607</t>
+          <t>25538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50493</t>
+          <t>50509</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15681</t>
+          <t>16164</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35940</t>
+          <t>37342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46150</t>
+          <t>46719</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77343</t>
+          <t>77087</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>17201</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9520</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28605</t>
+          <t>26719</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16786</t>
+          <t>17055</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>37478</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90865</t>
+          <t>89388</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128767</t>
+          <t>128799</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54992</t>
+          <t>55189</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87065</t>
+          <t>86461</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155731</t>
+          <t>154415</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>204139</t>
+          <t>204807</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>296541</t>
+          <t>296456</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>344193</t>
+          <t>346511</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>276869</t>
+          <t>279412</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>320009</t>
+          <t>322849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>590205</t>
+          <t>592428</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>651304</t>
+          <t>654641</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,69%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84605</t>
+          <t>87038</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>122466</t>
+          <t>124046</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69824</t>
+          <t>69413</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103262</t>
+          <t>105645</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>165768</t>
+          <t>164087</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>217406</t>
+          <t>215895</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>17114</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>997</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>8053</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19474</t>
+          <t>20394</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60742</t>
+          <t>62850</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93886</t>
+          <t>96223</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84648</t>
+          <t>85618</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126857</t>
+          <t>125462</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>155097</t>
+          <t>157909</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>212057</t>
+          <t>207545</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>613340</t>
+          <t>614042</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>706835</t>
+          <t>709478</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>573676</t>
+          <t>577783</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>662268</t>
+          <t>664724</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1219561</t>
+          <t>1215180</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1345986</t>
+          <t>1341065</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1738550</t>
+          <t>1735999</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1854640</t>
+          <t>1847720</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1953737</t>
+          <t>1955627</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2064585</t>
+          <t>2064424</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3722774</t>
+          <t>3723715</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3880925</t>
+          <t>3885786</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,47%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>610570</t>
+          <t>620467</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>711059</t>
+          <t>711264</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>546641</t>
+          <t>548900</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>638788</t>
+          <t>640127</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1191376</t>
+          <t>1192762</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1325381</t>
+          <t>1320768</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60201</t>
+          <t>60993</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>95522</t>
+          <t>96812</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34044</t>
+          <t>36330</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>62340</t>
+          <t>64576</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>102838</t>
+          <t>100901</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>149894</t>
+          <t>148019</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26319</t>
+          <t>27075</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51831</t>
+          <t>51818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32378</t>
+          <t>32704</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58462</t>
+          <t>58866</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65805</t>
+          <t>66572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102076</t>
+          <t>104156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>191913</t>
+          <t>193496</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246622</t>
+          <t>248710</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285277</t>
+          <t>283471</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>346287</t>
+          <t>347604</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>490020</t>
+          <t>496591</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575008</t>
+          <t>582920</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>497432</t>
+          <t>498338</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>562753</t>
+          <t>561735</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>701761</t>
+          <t>699889</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>775684</t>
+          <t>774092</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1222190</t>
+          <t>1215480</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1320168</t>
+          <t>1315383</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,21%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>134615</t>
+          <t>132847</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>184479</t>
+          <t>182825</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>193817</t>
+          <t>195533</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>248087</t>
+          <t>254800</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>347403</t>
+          <t>344352</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>421106</t>
+          <t>422475</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12737</t>
+          <t>11860</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30624</t>
+          <t>30270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24974</t>
+          <t>22485</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22894</t>
+          <t>23596</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45361</t>
+          <t>47475</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22914</t>
+          <t>23630</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47150</t>
+          <t>48832</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>18611</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40644</t>
+          <t>41007</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48302</t>
+          <t>46671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79102</t>
+          <t>80105</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>211874</t>
+          <t>211964</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>271406</t>
+          <t>274611</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>213805</t>
+          <t>212750</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>270381</t>
+          <t>272789</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>441618</t>
+          <t>442343</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>524536</t>
+          <t>524610</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1087661</t>
+          <t>1090375</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1178232</t>
+          <t>1178604</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>968765</t>
+          <t>966881</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1051929</t>
+          <t>1052095</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2086297</t>
+          <t>2083628</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2207703</t>
+          <t>2212160</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,55%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>465805</t>
+          <t>468821</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>548405</t>
+          <t>547541</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>399682</t>
+          <t>397573</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>477044</t>
+          <t>470063</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>893188</t>
+          <t>891793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>998244</t>
+          <t>1000200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30682</t>
+          <t>30863</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58161</t>
+          <t>56434</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25349</t>
+          <t>25515</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49524</t>
+          <t>50235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63194</t>
+          <t>63292</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99818</t>
+          <t>98242</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16809</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21051</t>
+          <t>21328</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12253</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31759</t>
+          <t>30656</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54980</t>
+          <t>54325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87668</t>
+          <t>87682</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58675</t>
+          <t>59309</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92616</t>
+          <t>92921</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>121198</t>
+          <t>123346</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>168650</t>
+          <t>171419</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>253893</t>
+          <t>252320</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>297806</t>
+          <t>298317</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>247942</t>
+          <t>249700</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>294464</t>
+          <t>296889</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>514450</t>
+          <t>515055</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>580302</t>
+          <t>579552</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,67%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>106557</t>
+          <t>107926</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>147300</t>
+          <t>147508</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>78611</t>
+          <t>77712</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117696</t>
+          <t>115747</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>196533</t>
+          <t>197102</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>249719</t>
+          <t>250531</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>974</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62985</t>
+          <t>62479</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100212</t>
+          <t>99366</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66481</t>
+          <t>67577</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>103608</t>
+          <t>103795</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>139182</t>
+          <t>137720</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>189558</t>
+          <t>193226</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>489350</t>
+          <t>486600</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>576460</t>
+          <t>573182</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>585294</t>
+          <t>587806</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>676902</t>
+          <t>681379</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1096918</t>
+          <t>1097838</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1223324</t>
+          <t>1226544</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1875506</t>
+          <t>1887494</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1998201</t>
+          <t>2003962</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1955711</t>
+          <t>1961361</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2083966</t>
+          <t>2084896</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3884339</t>
+          <t>3888244</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4051469</t>
+          <t>4047310</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,2%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>742316</t>
+          <t>745626</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>842162</t>
+          <t>844156</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>704276</t>
+          <t>704026</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>806014</t>
+          <t>808327</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1471819</t>
+          <t>1476507</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1623072</t>
+          <t>1623320</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47848</t>
+          <t>47068</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>79502</t>
+          <t>81327</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,82 +6205,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>52998</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>40357</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>70645</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>116314</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>97272</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>140477</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>52998</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>39784</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>68990</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>116314</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>97820</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>137829</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19301</t>
+          <t>19553</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40140</t>
+          <t>39606</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14755</t>
+          <t>15158</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35519</t>
+          <t>36215</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39547</t>
+          <t>39748</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67991</t>
+          <t>67238</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68044</t>
+          <t>67840</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103013</t>
+          <t>101649</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>122686</t>
+          <t>123414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>169936</t>
+          <t>169926</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>202492</t>
+          <t>199452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>259717</t>
+          <t>257754</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>378025</t>
+          <t>380537</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>434293</t>
+          <t>431433</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>528098</t>
+          <t>520578</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>591777</t>
+          <t>588079</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>924735</t>
+          <t>923733</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1008907</t>
+          <t>1007512</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,88%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>182817</t>
+          <t>185675</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>235094</t>
+          <t>233181</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>212730</t>
+          <t>212191</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>267140</t>
+          <t>269444</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>410321</t>
+          <t>410900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>484324</t>
+          <t>486974</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16245</t>
+          <t>17101</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36462</t>
+          <t>37220</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33607</t>
+          <t>32161</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34765</t>
+          <t>34860</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62154</t>
+          <t>60793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>21482</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44759</t>
+          <t>45666</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>23174</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46941</t>
+          <t>46241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49162</t>
+          <t>48098</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81206</t>
+          <t>81339</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>221312</t>
+          <t>221535</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282767</t>
+          <t>284125</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>250238</t>
+          <t>248006</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>312373</t>
+          <t>312166</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>486881</t>
+          <t>490751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>575383</t>
+          <t>575852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1171487</t>
+          <t>1172877</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1265746</t>
+          <t>1270321</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1127170</t>
+          <t>1129874</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1215103</t>
+          <t>1215465</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2325893</t>
+          <t>2320515</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2459953</t>
+          <t>2448102</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,58%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>475979</t>
+          <t>472703</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>556035</t>
+          <t>557099</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>425481</t>
+          <t>427473</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>506614</t>
+          <t>501204</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>923687</t>
+          <t>922851</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1037075</t>
+          <t>1033118</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34850</t>
+          <t>33903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61420</t>
+          <t>60845</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23765</t>
+          <t>24048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49617</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63332</t>
+          <t>64074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99096</t>
+          <t>100182</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17109</t>
+          <t>17885</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>883</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20159</t>
+          <t>20726</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51545</t>
+          <t>51959</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82296</t>
+          <t>86622</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>66849</t>
+          <t>66992</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99403</t>
+          <t>100486</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125663</t>
+          <t>126832</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>171650</t>
+          <t>172349</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>305325</t>
+          <t>305795</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>352642</t>
+          <t>355442</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>298481</t>
+          <t>300243</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>344176</t>
+          <t>346080</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>620730</t>
+          <t>619259</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>685495</t>
+          <t>685167</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,69%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>111116</t>
+          <t>111948</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>154936</t>
+          <t>153837</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>109264</t>
+          <t>106381</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>149023</t>
+          <t>149547</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>232612</t>
+          <t>236069</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>289907</t>
+          <t>293012</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>17032</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18219</t>
+          <t>17525</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27588</t>
+          <t>29160</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53211</t>
+          <t>53543</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88539</t>
+          <t>88958</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45632</t>
+          <t>45172</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75656</t>
+          <t>74957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>107059</t>
+          <t>106782</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>152845</t>
+          <t>152318</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>364939</t>
+          <t>361443</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>441949</t>
+          <t>439983</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>465606</t>
+          <t>469919</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>549191</t>
+          <t>550319</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>858010</t>
+          <t>853699</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>971787</t>
+          <t>971737</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1898105</t>
+          <t>1898551</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2010453</t>
+          <t>2015952</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1995528</t>
+          <t>1991188</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2112275</t>
+          <t>2107341</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3924717</t>
+          <t>3926355</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4098190</t>
+          <t>4092723</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,53%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>806750</t>
+          <t>808113</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>905836</t>
+          <t>910192</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>777587</t>
+          <t>775404</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>882870</t>
+          <t>878453</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1613455</t>
+          <t>1611791</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1761821</t>
+          <t>1758284</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>64105</t>
+          <t>63863</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>99429</t>
+          <t>99787</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49124</t>
+          <t>49898</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>83076</t>
+          <t>82911</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>122969</t>
+          <t>123782</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>169790</t>
+          <t>170258</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17738</t>
+          <t>20307</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>13721</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17702</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12070</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26383</t>
+          <t>28305</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42947</t>
+          <t>46821</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32213</t>
+          <t>35073</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55279</t>
+          <t>59064</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>82402</t>
+          <t>82436</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69869</t>
+          <t>70447</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>102304</t>
+          <t>95803</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>125349</t>
+          <t>129257</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107838</t>
+          <t>111667</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147517</t>
+          <t>148537</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>286873</t>
+          <t>319099</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>265694</t>
+          <t>294904</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>306733</t>
+          <t>341362</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>439077</t>
+          <t>474553</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>416801</t>
+          <t>450626</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>460166</t>
+          <t>495307</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>725949</t>
+          <t>793652</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>696161</t>
+          <t>762184</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>755355</t>
+          <t>825767</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>58,96%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>154637</t>
+          <t>178788</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>136315</t>
+          <t>158426</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>175365</t>
+          <t>203566</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>211165</t>
+          <t>238176</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>192429</t>
+          <t>219316</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229726</t>
+          <t>261079</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>365802</t>
+          <t>416964</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>340860</t>
+          <t>387385</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>396782</t>
+          <t>447966</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20001</t>
+          <t>22617</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>14922</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29869</t>
+          <t>33716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>18466</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10571</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22553</t>
+          <t>26155</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>35644</t>
+          <t>41084</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26838</t>
+          <t>31382</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46153</t>
+          <t>53887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18006</t>
+          <t>19925</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33897</t>
+          <t>36974</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24921</t>
+          <t>29889</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15362</t>
+          <t>20804</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37530</t>
+          <t>43933</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>42928</t>
+          <t>49814</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29267</t>
+          <t>37303</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61614</t>
+          <t>67984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>186902</t>
+          <t>194170</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131433</t>
+          <t>167882</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>224133</t>
+          <t>225680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>201012</t>
+          <t>216638</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150491</t>
+          <t>191204</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>238942</t>
+          <t>242603</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>387915</t>
+          <t>410809</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>313382</t>
+          <t>373066</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>445341</t>
+          <t>449172</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1159693</t>
+          <t>1243523</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>853159</t>
+          <t>1192364</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1321335</t>
+          <t>1299200</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1204157</t>
+          <t>1215994</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>911622</t>
+          <t>1175839</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1356918</t>
+          <t>1259133</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2363851</t>
+          <t>2459517</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1896788</t>
+          <t>2394445</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2619359</t>
+          <t>2529301</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,49%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>611317</t>
+          <t>687920</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>443892</t>
+          <t>637048</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>705293</t>
+          <t>739703</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>752205</t>
+          <t>635112</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>580190</t>
+          <t>593520</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1118264</t>
+          <t>674937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1363523</t>
+          <t>1323031</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1149992</t>
+          <t>1259765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1844958</t>
+          <t>1391082</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>31,62%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>313403</t>
+          <t>84094</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68901</t>
+          <t>65699</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>802210</t>
+          <t>111277</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>54410</t>
+          <t>72634</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>57502</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72337</t>
+          <t>92944</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>367813</t>
+          <t>156728</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119843</t>
+          <t>132156</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1037982</t>
+          <t>187560</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2289322</t>
+          <t>2229632</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2289322</t>
+          <t>2229632</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2289322</t>
+          <t>2229632</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2236706</t>
+          <t>2170266</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2236706</t>
+          <t>2170266</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2236706</t>
+          <t>2170266</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4526029</t>
+          <t>4399898</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4526029</t>
+          <t>4399898</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4526029</t>
+          <t>4399898</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14770</t>
+          <t>16436</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,17 +11004,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>13458</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22013</t>
+          <t>24217</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>85282</t>
+          <t>81626</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67075</t>
+          <t>63400</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>113065</t>
+          <t>98621</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>84429</t>
+          <t>92587</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71207</t>
+          <t>77821</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99862</t>
+          <t>110113</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>169711</t>
+          <t>174213</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>148447</t>
+          <t>150678</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>200861</t>
+          <t>197310</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>328594</t>
+          <t>358043</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>299446</t>
+          <t>329244</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>355985</t>
+          <t>388708</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>369586</t>
+          <t>401234</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>347891</t>
+          <t>376600</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>391023</t>
+          <t>425329</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>698180</t>
+          <t>759277</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>662351</t>
+          <t>721259</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>734203</t>
+          <t>793908</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>54,89%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>196389</t>
+          <t>225503</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>172634</t>
+          <t>198889</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>222086</t>
+          <t>253301</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>184810</t>
+          <t>210748</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>164434</t>
+          <t>188721</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>203972</t>
+          <t>234896</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>381198</t>
+          <t>436251</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>347629</t>
+          <t>402341</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>415916</t>
+          <t>469873</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>28282</t>
+          <t>37918</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18288</t>
+          <t>24038</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46109</t>
+          <t>56446</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>24361</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10696</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23802</t>
+          <t>34364</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>44538</t>
+          <t>62279</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32736</t>
+          <t>47242</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63133</t>
+          <t>85126</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>36564</t>
+          <t>39626</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24330</t>
+          <t>28068</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52178</t>
+          <t>55962</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>37524</t>
+          <t>44242</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27297</t>
+          <t>33566</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51365</t>
+          <t>58075</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>74088</t>
+          <t>83868</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57832</t>
+          <t>66860</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93065</t>
+          <t>102815</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>315131</t>
+          <t>322617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>239442</t>
+          <t>288705</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>360282</t>
+          <t>364521</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>367844</t>
+          <t>391661</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>305425</t>
+          <t>361858</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>411212</t>
+          <t>425006</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>682975</t>
+          <t>714279</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>592107</t>
+          <t>668060</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>750834</t>
+          <t>763035</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1775160</t>
+          <t>1920666</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1349783</t>
+          <t>1853318</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1934716</t>
+          <t>1981853</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2012820</t>
+          <t>2091781</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1649705</t>
+          <t>2036593</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2165710</t>
+          <t>2147456</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3787980</t>
+          <t>4012447</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3169219</t>
+          <t>3931705</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4028583</t>
+          <t>4103672</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,63%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>962343</t>
+          <t>1092211</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>728916</t>
+          <t>1031930</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1054111</t>
+          <t>1156189</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1148180</t>
+          <t>1084035</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>975290</t>
+          <t>1036805</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1589489</t>
+          <t>1132731</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2110523</t>
+          <t>2176246</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1881397</t>
+          <t>2088788</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2632989</t>
+          <t>2253867</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>361686</t>
+          <t>144629</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>119481</t>
+          <t>119593</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1137072</t>
+          <t>177013</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>86309</t>
+          <t>115462</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>68196</t>
+          <t>97801</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>104785</t>
+          <t>136574</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>447995</t>
+          <t>260091</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>203733</t>
+          <t>228116</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1487159</t>
+          <t>295764</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3450884</t>
+          <t>3519749</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3450884</t>
+          <t>3519749</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3450884</t>
+          <t>3519749</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3652677</t>
+          <t>3727181</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3652677</t>
+          <t>3727181</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3652677</t>
+          <t>3727181</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7103561</t>
+          <t>7246930</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7103561</t>
+          <t>7246930</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7103561</t>
+          <t>7246930</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
